--- a/Resultados/7d8_mantem3/jogador_cauteloso.xlsx
+++ b/Resultados/7d8_mantem3/jogador_cauteloso.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$1:$C$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Distribuicao_conjunta'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Distribuicao_conjunta'!$A$1:$E$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Acertos'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desafios'!$A$1:$C$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Adaptacoes'!$A$1:$C$5</definedName>
@@ -461,7 +461,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4.010036468505859</v>
+        <v>3.193537712097168</v>
       </c>
     </row>
     <row r="13">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -678,7 +678,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.316906334119267</v>
+        <v>0.7627913000533226</v>
       </c>
     </row>
     <row r="16">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.14756539426704</v>
+        <v>0.8733792418264374</v>
       </c>
     </row>
     <row r="17">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.403995513916016</v>
+        <v>2.168557167053223</v>
       </c>
     </row>
     <row r="22">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.9317583278607344</v>
+        <v>0.691167224415949</v>
       </c>
     </row>
     <row r="25">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.9652762961249667</v>
+        <v>0.8313646759490981</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.569382667541504</v>
+        <v>2.385881423950195</v>
       </c>
     </row>
     <row r="31">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.6317312267192392</v>
+        <v>0.3932269506003649</v>
       </c>
     </row>
     <row r="34">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.7948152154552901</v>
+        <v>0.6270781056617788</v>
       </c>
     </row>
     <row r="35">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1058,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1208,10 +1208,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>37695</v>
+        <v>75390</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.79743766784668</v>
+        <v>3.594875335693359</v>
       </c>
     </row>
     <row r="9">
@@ -1242,10 +1242,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>693</v>
+        <v>735</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.03304481506347656</v>
+        <v>0.03504753112792969</v>
       </c>
     </row>
     <row r="11">
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.002336502075195312</v>
+        <v>0.0026702880859375</v>
       </c>
     </row>
     <row r="13">
@@ -1327,10 +1327,10 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>56630</v>
+        <v>18935</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2.700328826904297</v>
+        <v>0.9028911590576172</v>
       </c>
     </row>
     <row r="16">
@@ -1344,10 +1344,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8862</v>
+        <v>17724</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.4225730895996094</v>
+        <v>0.8451461791992188</v>
       </c>
     </row>
     <row r="17">
@@ -1361,10 +1361,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3395</v>
+        <v>3353</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.1618862152099609</v>
+        <v>0.1598834991455078</v>
       </c>
     </row>
     <row r="18">
@@ -1378,10 +1378,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>26607</v>
+        <v>35511</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.268720626831055</v>
+        <v>1.693296432495117</v>
       </c>
     </row>
     <row r="19">
@@ -1395,10 +1395,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>44121</v>
+        <v>176484</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2.103853225708008</v>
+        <v>8.415412902832031</v>
       </c>
     </row>
     <row r="20">
@@ -1412,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.00133514404296875</v>
+        <v>0.001001358032226562</v>
       </c>
     </row>
     <row r="21">
@@ -1429,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1428</v>
+        <v>1470</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.06809234619140625</v>
+        <v>0.07009506225585938</v>
       </c>
     </row>
     <row r="22">
@@ -1446,10 +1446,10 @@
         <v>2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1323</v>
+        <v>2688</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.06308555603027344</v>
+        <v>0.128173828125</v>
       </c>
     </row>
     <row r="23">
@@ -1480,10 +1480,10 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.02102851867675781</v>
+        <v>0.02303123474121094</v>
       </c>
     </row>
     <row r="25">
@@ -1514,10 +1514,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>26811</v>
+        <v>53719</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1.278448104858398</v>
+        <v>2.561521530151367</v>
       </c>
     </row>
     <row r="27">
@@ -1531,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>25263</v>
+        <v>16401</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.204633712768555</v>
+        <v>0.7820606231689453</v>
       </c>
     </row>
     <row r="28">
@@ -1548,10 +1548,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>44121</v>
+        <v>141792</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2.103853225708008</v>
+        <v>6.76116943359375</v>
       </c>
     </row>
     <row r="29">
@@ -1565,10 +1565,10 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>12215</v>
+        <v>3311</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.5824565887451172</v>
+        <v>0.1578807830810547</v>
       </c>
     </row>
     <row r="30">
@@ -1582,10 +1582,10 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>182609</v>
+        <v>127169</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>8.707475662231445</v>
+        <v>6.06389045715332</v>
       </c>
     </row>
     <row r="31">
@@ -1599,10 +1599,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>37695</v>
+        <v>211904</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.79743766784668</v>
+        <v>10.1043701171875</v>
       </c>
     </row>
     <row r="32">
@@ -1616,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>981</v>
+        <v>939</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.04677772521972656</v>
+        <v>0.04477500915527344</v>
       </c>
     </row>
     <row r="33">
@@ -1633,10 +1633,10 @@
         <v>1</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14861</v>
+        <v>16828</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.7086277008056641</v>
+        <v>0.8024215698242188</v>
       </c>
     </row>
     <row r="34">
@@ -1650,10 +1650,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>38535</v>
+        <v>85932</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.837491989135742</v>
+        <v>4.097557067871094</v>
       </c>
     </row>
     <row r="35">
@@ -1667,10 +1667,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>26811</v>
+        <v>264168</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.278448104858398</v>
+        <v>12.59651184082031</v>
       </c>
     </row>
     <row r="36">
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>735</v>
+        <v>693</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.03504753112792969</v>
+        <v>0.03304481506347656</v>
       </c>
     </row>
     <row r="37">
@@ -1701,10 +1701,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3045</v>
+        <v>4389</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.1451969146728516</v>
+        <v>0.2092838287353516</v>
       </c>
     </row>
     <row r="38">
@@ -1718,10 +1718,10 @@
         <v>2</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>651</v>
+        <v>2604</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.03104209899902344</v>
+        <v>0.1241683959960938</v>
       </c>
     </row>
     <row r="39">
@@ -1752,10 +1752,10 @@
         <v>1</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>399</v>
+        <v>798</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.01902580261230469</v>
+        <v>0.03805160522460938</v>
       </c>
     </row>
     <row r="41">
@@ -1780,16 +1780,16 @@
         <v>4</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>85967</v>
+        <v>233051</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4.099225997924805</v>
+        <v>11.11273765563965</v>
       </c>
     </row>
     <row r="43">
@@ -1797,16 +1797,16 @@
         <v>4</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>76923</v>
+        <v>8862</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>3.667974472045898</v>
+        <v>0.4225730895996094</v>
       </c>
     </row>
     <row r="44">
@@ -1814,16 +1814,16 @@
         <v>4</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>212821</v>
+        <v>416248</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>10.14809608459473</v>
+        <v>19.84825134277344</v>
       </c>
     </row>
     <row r="45">
@@ -1831,16 +1831,16 @@
         <v>4</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>3332</v>
+        <v>3311</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.1588821411132812</v>
+        <v>0.1578807830810547</v>
       </c>
     </row>
     <row r="46">
@@ -1848,16 +1848,16 @@
         <v>4</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>51828</v>
+        <v>32389</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2.471351623535156</v>
+        <v>1.544427871704102</v>
       </c>
     </row>
     <row r="47">
@@ -1865,16 +1865,16 @@
         <v>4</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>222481</v>
+        <v>65604</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>10.60872077941895</v>
+        <v>3.128242492675781</v>
       </c>
     </row>
     <row r="48">
@@ -1882,16 +1882,16 @@
         <v>4</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4655</v>
+        <v>1323</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.2219676971435547</v>
+        <v>0.06308555603027344</v>
       </c>
     </row>
     <row r="49">
@@ -1899,16 +1899,16 @@
         <v>4</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>24829</v>
+        <v>2604</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.183938980102539</v>
+        <v>0.1241683959960938</v>
       </c>
     </row>
     <row r="50">
@@ -1916,67 +1916,67 @@
         <v>4</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>16401</v>
+        <v>399</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.7820606231689453</v>
+        <v>0.01902580261230469</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1722</v>
+        <v>13363</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.08211135864257812</v>
+        <v>0.6371974945068359</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1302</v>
+        <v>4431</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.06208419799804688</v>
+        <v>0.2112865447998047</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>399</v>
+        <v>26726</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.01902580261230469</v>
+        <v>1.274394989013672</v>
       </c>
     </row>
     <row r="54">
@@ -1984,207 +1984,37 @@
         <v>5</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>189651</v>
+        <v>651</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>9.043264389038086</v>
+        <v>0.03104209899902344</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4431</v>
+        <v>3991</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.2112865447998047</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>377405</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>17.99607276916504</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>9513</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>0.4536151885986328</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>46165</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>2.201318740844727</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>5733</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0.2733707427978516</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>13363</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.6371974945068359</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>651</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0.03104209899902344</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>97119</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>4.63099479675293</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>16401</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0.7820606231689453</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>13363</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0.6371974945068359</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>3991</v>
-      </c>
-      <c r="E65" s="3" t="n">
         <v>0.1903057098388672</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2236,10 +2066,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46284</v>
+        <v>84028</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.206993103027344</v>
+        <v>4.006767272949219</v>
       </c>
     </row>
     <row r="4">
@@ -2247,10 +2077,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>143556</v>
+        <v>257390</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6.845283508300781</v>
+        <v>12.27331161499023</v>
       </c>
     </row>
     <row r="5">
@@ -2258,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>415272</v>
+        <v>931187</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19.80171203613281</v>
+        <v>44.40245628356934</v>
       </c>
     </row>
     <row r="6">
@@ -2269,10 +2099,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>702660</v>
+        <v>763791</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>33.50543975830078</v>
+        <v>36.4203929901123</v>
       </c>
     </row>
     <row r="7">
@@ -2280,10 +2110,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>646912</v>
+        <v>45171</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>30.84716796875</v>
+        <v>2.153921127319336</v>
       </c>
     </row>
     <row r="8">
@@ -2291,10 +2121,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>130874</v>
+        <v>3991</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6.240558624267578</v>
+        <v>0.1903057098388672</v>
       </c>
     </row>
   </sheetData>
@@ -2339,10 +2169,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>399548</v>
+        <v>53719</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>19.05193328857422</v>
+        <v>2.561521530151367</v>
       </c>
     </row>
     <row r="3">
@@ -2350,10 +2180,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>758016</v>
+        <v>391895</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>36.14501953125</v>
+        <v>18.68700981140137</v>
       </c>
     </row>
     <row r="4">
@@ -2361,10 +2191,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>648004</v>
+        <v>820827</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30.89923858642578</v>
+        <v>39.14008140563965</v>
       </c>
     </row>
     <row r="5">
@@ -2372,10 +2202,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>278016</v>
+        <v>811095</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>13.2568359375</v>
+        <v>38.67602348327637</v>
       </c>
     </row>
     <row r="6">
@@ -2383,10 +2213,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11648</v>
+        <v>17248</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.555419921875</v>
+        <v>0.82244873046875</v>
       </c>
     </row>
     <row r="7">
@@ -2394,10 +2224,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1792</v>
+        <v>2240</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.08544921875</v>
+        <v>0.1068115234375</v>
       </c>
     </row>
     <row r="8">
@@ -2453,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>163679</v>
+        <v>16384</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7.80482292175293</v>
+        <v>0.78125</v>
       </c>
     </row>
     <row r="3">
@@ -2464,10 +2294,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>817355</v>
+        <v>114688</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>38.97452354431152</v>
+        <v>5.46875</v>
       </c>
     </row>
     <row r="4">
@@ -2475,10 +2305,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>874475</v>
+        <v>1009372</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>41.69821739196777</v>
+        <v>48.13060760498047</v>
       </c>
     </row>
     <row r="5">
@@ -2486,10 +2316,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>241643</v>
+        <v>956708</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>11.52243614196777</v>
+        <v>45.61939239501953</v>
       </c>
     </row>
   </sheetData>
@@ -2563,10 +2393,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46284</v>
+        <v>84028</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.206993103027344</v>
+        <v>4.006767272949219</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>99.4471549987793</v>
@@ -2580,16 +2410,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>143556</v>
+        <v>257390</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6.845283508300781</v>
+        <v>12.27331161499023</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>97.24016189575195</v>
+        <v>95.44038772583008</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2.759838104248047</v>
+        <v>4.559612274169922</v>
       </c>
     </row>
     <row r="5">
@@ -2597,16 +2427,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>415272</v>
+        <v>931187</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>19.80171203613281</v>
+        <v>44.40245628356934</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>90.39487838745117</v>
+        <v>83.16707611083984</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>9.605121612548828</v>
+        <v>16.83292388916016</v>
       </c>
     </row>
     <row r="6">
@@ -2614,16 +2444,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>702660</v>
+        <v>763791</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>33.50543975830078</v>
+        <v>36.4203929901123</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>70.59316635131836</v>
+        <v>38.76461982727051</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>29.40683364868164</v>
+        <v>61.23538017272949</v>
       </c>
     </row>
     <row r="7">
@@ -2631,16 +2461,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>646912</v>
+        <v>45171</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>30.84716796875</v>
+        <v>2.153921127319336</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>37.08772659301758</v>
+        <v>2.344226837158203</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>62.91227340698242</v>
+        <v>97.6557731628418</v>
       </c>
     </row>
     <row r="8">
@@ -2648,16 +2478,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>130874</v>
+        <v>3991</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6.240558624267578</v>
+        <v>0.1903057098388672</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>6.240558624267578</v>
+        <v>0.1903057098388672</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>93.75944137573242</v>
+        <v>99.80969429016113</v>
       </c>
     </row>
   </sheetData>
@@ -2750,13 +2580,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1109188</v>
+        <v>1302059</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.5289020538330078</v>
+        <v>0.6208701133728027</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>17.63006846110026</v>
+        <v>20.69567044576009</v>
       </c>
     </row>
     <row r="6">
@@ -2778,13 +2608,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1560002</v>
+        <v>1302059</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.7438669204711914</v>
+        <v>0.6208701133728027</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>24.79556401570638</v>
+        <v>20.69567044576009</v>
       </c>
     </row>
     <row r="8">
@@ -2792,13 +2622,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>920580</v>
+        <v>1029052</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.4389667510986328</v>
+        <v>0.4906902313232422</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>14.63222503662109</v>
+        <v>16.35634104410807</v>
       </c>
     </row>
     <row r="9">
@@ -2806,13 +2636,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1820794</v>
+        <v>1777394</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.8682222366333008</v>
+        <v>0.8475275039672852</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>28.94074122111003</v>
+        <v>28.2509167989095</v>
       </c>
     </row>
   </sheetData>
